--- a/outputs/daily/hr_rankings_2026-08-29_remaining.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-29_remaining.xlsx
@@ -21520,7 +21520,7 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>32.2</v>
+        <v>32.4</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
         <v>50</v>
       </c>
       <c r="U76" t="n">
-        <v>19.5</v>
+        <v>24.9</v>
       </c>
       <c r="V76" t="inlineStr">
         <is>
@@ -21609,12 +21609,12 @@
       </c>
       <c r="AH76" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ76" t="inlineStr">
@@ -21624,7 +21624,7 @@
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL76" t="inlineStr">
